--- a/brainfuck/bf-signature.xlsx
+++ b/brainfuck/bf-signature.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\bf-signature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Documents\GitHub\bf-signature\brainfuck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6761EB24-3B42-49F8-A105-E565C3C9BF23}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044EBD35-D27D-4C19-AA13-B39F0C8A1307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="642" xr2:uid="{AE3D3994-95C1-48E7-B5B4-B402D07D41B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="642" xr2:uid="{AE3D3994-95C1-48E7-B5B4-B402D07D41B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -89,7 +83,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="\+0;\-0"/>
+    <numFmt numFmtId="164" formatCode="\+0;\-0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -179,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -217,18 +211,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -244,7 +235,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -688,16 +679,16 @@
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-      <c r="H2" s="16">
+      <c r="H2" s="15">
         <v>3</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="15">
         <v>1</v>
       </c>
       <c r="J2" s="8">
         <v>1</v>
       </c>
-      <c r="K2" s="17" t="str">
+      <c r="K2" s="16" t="str">
         <f t="shared" ref="K2:K26" si="0">_xlfn.CONCAT(REPT(IF(H2&gt;0,"&gt;","&lt;"),ABS(H2)),REPT(IF(I2&gt;0,"+","-"),ABS(I2)),".")</f>
         <v>&gt;&gt;&gt;+.</v>
       </c>
@@ -711,16 +702,16 @@
       </c>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
-      <c r="S2" s="16">
+      <c r="S2" s="15">
         <v>3</v>
       </c>
-      <c r="T2" s="16">
+      <c r="T2" s="15">
         <v>1</v>
       </c>
       <c r="U2" s="8">
         <v>1</v>
       </c>
-      <c r="V2" s="17" t="str">
+      <c r="V2" s="16" t="str">
         <f t="shared" ref="V2:V26" si="1">_xlfn.CONCAT(REPT(IF(S2&gt;0,"&gt;","&lt;"),ABS(S2)),REPT(IF(T2&gt;0,"+","-"),ABS(T2)),".")</f>
         <v>&gt;&gt;&gt;+.</v>
       </c>
@@ -734,16 +725,16 @@
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
-      <c r="AD2" s="16">
+      <c r="AD2" s="15">
         <v>2</v>
       </c>
-      <c r="AE2" s="16">
+      <c r="AE2" s="15">
         <v>1</v>
       </c>
       <c r="AF2" s="8">
         <v>1</v>
       </c>
-      <c r="AG2" s="17" t="str">
+      <c r="AG2" s="16" t="str">
         <f t="shared" ref="AG2:AG26" si="2">_xlfn.CONCAT(REPT(IF(AD2&gt;0,"&gt;","&lt;"),ABS(AD2)),REPT(IF(AE2&gt;0,"+","-"),ABS(AE2)),".")</f>
         <v>&gt;&gt;+.</v>
       </c>
@@ -755,12 +746,12 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
-      <c r="AO2" s="16"/>
-      <c r="AP2" s="16"/>
-      <c r="AQ2" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR2" s="17" t="str">
+      <c r="AO2" s="15"/>
+      <c r="AP2" s="15"/>
+      <c r="AQ2" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="16" t="str">
         <f t="shared" ref="AR2:AR26" si="3">_xlfn.CONCAT(REPT(IF(AO2&gt;0,"&gt;","&lt;"),ABS(AO2)),REPT(IF(AP2&gt;0,"+","-"),ABS(AP2)),".")</f>
         <v>.</v>
       </c>
@@ -779,16 +770,16 @@
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <v>0</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <v>-3</v>
       </c>
       <c r="J3" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="17" t="str">
+      <c r="K3" s="16" t="str">
         <f t="shared" si="0"/>
         <v>---.</v>
       </c>
@@ -802,16 +793,16 @@
       </c>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="16">
+      <c r="S3" s="15">
         <v>0</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="15">
         <v>-3</v>
       </c>
       <c r="U3" s="8">
         <v>1</v>
       </c>
-      <c r="V3" s="17" t="str">
+      <c r="V3" s="16" t="str">
         <f t="shared" si="1"/>
         <v>---.</v>
       </c>
@@ -825,16 +816,16 @@
       <c r="AA3" s="5"/>
       <c r="AB3" s="5"/>
       <c r="AC3" s="5"/>
-      <c r="AD3" s="16">
+      <c r="AD3" s="15">
         <v>0</v>
       </c>
-      <c r="AE3" s="16">
+      <c r="AE3" s="15">
         <v>-3</v>
       </c>
       <c r="AF3" s="8">
         <v>1</v>
       </c>
-      <c r="AG3" s="17" t="str">
+      <c r="AG3" s="16" t="str">
         <f t="shared" si="2"/>
         <v>---.</v>
       </c>
@@ -846,12 +837,12 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
       <c r="AN3" s="5"/>
-      <c r="AO3" s="16"/>
-      <c r="AP3" s="16"/>
-      <c r="AQ3" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR3" s="17" t="str">
+      <c r="AO3" s="15"/>
+      <c r="AP3" s="15"/>
+      <c r="AQ3" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -870,16 +861,16 @@
         <v>110</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="16">
-        <v>1</v>
-      </c>
-      <c r="I4" s="16">
+      <c r="H4" s="15">
+        <v>1</v>
+      </c>
+      <c r="I4" s="15">
         <v>2</v>
       </c>
       <c r="J4" s="8">
         <v>1</v>
       </c>
-      <c r="K4" s="17" t="str">
+      <c r="K4" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;++.</v>
       </c>
@@ -893,16 +884,16 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
-      <c r="S4" s="16">
+      <c r="S4" s="15">
         <v>-1</v>
       </c>
-      <c r="T4" s="16">
+      <c r="T4" s="15">
         <v>2</v>
       </c>
       <c r="U4" s="8">
         <v>1</v>
       </c>
-      <c r="V4" s="17" t="str">
+      <c r="V4" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;++.</v>
       </c>
@@ -916,16 +907,16 @@
       </c>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
-      <c r="AD4" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="16">
+      <c r="AD4" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="15">
         <v>2</v>
       </c>
       <c r="AF4" s="8">
         <v>1</v>
       </c>
-      <c r="AG4" s="17" t="str">
+      <c r="AG4" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;++.</v>
       </c>
@@ -937,12 +928,12 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
-      <c r="AO4" s="16"/>
-      <c r="AP4" s="16"/>
-      <c r="AQ4" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR4" s="17" t="str">
+      <c r="AO4" s="15"/>
+      <c r="AP4" s="15"/>
+      <c r="AQ4" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -961,16 +952,16 @@
       <c r="G5" s="5">
         <v>105</v>
       </c>
-      <c r="H5" s="16">
-        <v>1</v>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="15">
+        <v>1</v>
+      </c>
+      <c r="I5" s="15">
         <v>-3</v>
       </c>
       <c r="J5" s="8">
         <v>1</v>
       </c>
-      <c r="K5" s="17" t="str">
+      <c r="K5" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;---.</v>
       </c>
@@ -984,16 +975,16 @@
         <v>105</v>
       </c>
       <c r="R5" s="5"/>
-      <c r="S5" s="16">
+      <c r="S5" s="15">
         <v>2</v>
       </c>
-      <c r="T5" s="16">
+      <c r="T5" s="15">
         <v>-3</v>
       </c>
       <c r="U5" s="8">
         <v>1</v>
       </c>
-      <c r="V5" s="17" t="str">
+      <c r="V5" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;&gt;---.</v>
       </c>
@@ -1007,16 +998,16 @@
         <v>105</v>
       </c>
       <c r="AC5" s="5"/>
-      <c r="AD5" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="16">
+      <c r="AD5" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="15">
         <v>-3</v>
       </c>
       <c r="AF5" s="8">
         <v>1</v>
       </c>
-      <c r="AG5" s="17" t="str">
+      <c r="AG5" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;---.</v>
       </c>
@@ -1028,12 +1019,12 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
-      <c r="AO5" s="16"/>
-      <c r="AP5" s="16"/>
-      <c r="AQ5" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR5" s="17" t="str">
+      <c r="AO5" s="15"/>
+      <c r="AP5" s="15"/>
+      <c r="AQ5" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1052,16 +1043,16 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <v>2</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="15">
         <v>4</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
       </c>
-      <c r="K6" s="17" t="str">
+      <c r="K6" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;++++.</v>
       </c>
@@ -1075,16 +1066,16 @@
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
-      <c r="S6" s="16">
+      <c r="S6" s="15">
         <v>-1</v>
       </c>
-      <c r="T6" s="16">
+      <c r="T6" s="15">
         <v>4</v>
       </c>
       <c r="U6" s="8">
         <v>1</v>
       </c>
-      <c r="V6" s="17" t="str">
+      <c r="V6" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;++++.</v>
       </c>
@@ -1098,16 +1089,16 @@
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
       <c r="AC6" s="5"/>
-      <c r="AD6" s="16">
+      <c r="AD6" s="15">
         <v>-2</v>
       </c>
-      <c r="AE6" s="16">
+      <c r="AE6" s="15">
         <v>4</v>
       </c>
       <c r="AF6" s="8">
         <v>1</v>
       </c>
-      <c r="AG6" s="17" t="str">
+      <c r="AG6" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;&lt;++++.</v>
       </c>
@@ -1119,12 +1110,12 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
-      <c r="AO6" s="16"/>
-      <c r="AP6" s="16"/>
-      <c r="AQ6" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR6" s="17" t="str">
+      <c r="AO6" s="15"/>
+      <c r="AP6" s="15"/>
+      <c r="AQ6" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1143,16 +1134,16 @@
       <c r="G7" s="5">
         <v>108</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <v>2</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>3</v>
       </c>
       <c r="J7" s="8">
         <v>1</v>
       </c>
-      <c r="K7" s="17" t="str">
+      <c r="K7" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;+++.</v>
       </c>
@@ -1166,16 +1157,16 @@
         <v>108</v>
       </c>
       <c r="R7" s="5"/>
-      <c r="S7" s="16">
-        <v>1</v>
-      </c>
-      <c r="T7" s="16">
+      <c r="S7" s="15">
+        <v>1</v>
+      </c>
+      <c r="T7" s="15">
         <v>3</v>
       </c>
       <c r="U7" s="8">
         <v>1</v>
       </c>
-      <c r="V7" s="17" t="str">
+      <c r="V7" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;+++.</v>
       </c>
@@ -1189,16 +1180,16 @@
         <v>108</v>
       </c>
       <c r="AC7" s="5"/>
-      <c r="AD7" s="16">
+      <c r="AD7" s="15">
         <v>2</v>
       </c>
-      <c r="AE7" s="16">
+      <c r="AE7" s="15">
         <v>3</v>
       </c>
       <c r="AF7" s="8">
         <v>1</v>
       </c>
-      <c r="AG7" s="17" t="str">
+      <c r="AG7" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;&gt;+++.</v>
       </c>
@@ -1210,12 +1201,12 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
-      <c r="AO7" s="16"/>
-      <c r="AP7" s="16"/>
-      <c r="AQ7" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR7" s="17" t="str">
+      <c r="AO7" s="15"/>
+      <c r="AP7" s="15"/>
+      <c r="AQ7" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1234,16 +1225,16 @@
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <v>2</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="8">
         <v>1</v>
       </c>
-      <c r="K8" s="17" t="str">
+      <c r="K8" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;.</v>
       </c>
@@ -1257,16 +1248,16 @@
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="16">
+      <c r="S8" s="15">
         <v>-1</v>
       </c>
-      <c r="T8" s="16">
+      <c r="T8" s="15">
         <v>0</v>
       </c>
       <c r="U8" s="8">
         <v>1</v>
       </c>
-      <c r="V8" s="17" t="str">
+      <c r="V8" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;.</v>
       </c>
@@ -1280,16 +1271,16 @@
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
-      <c r="AD8" s="16">
+      <c r="AD8" s="15">
         <v>-2</v>
       </c>
-      <c r="AE8" s="16">
+      <c r="AE8" s="15">
         <v>0</v>
       </c>
       <c r="AF8" s="8">
         <v>1</v>
       </c>
-      <c r="AG8" s="17" t="str">
+      <c r="AG8" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;&lt;.</v>
       </c>
@@ -1301,12 +1292,12 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
-      <c r="AO8" s="16"/>
-      <c r="AP8" s="16"/>
-      <c r="AQ8" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR8" s="17" t="str">
+      <c r="AO8" s="15"/>
+      <c r="AP8" s="15"/>
+      <c r="AQ8" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1325,16 +1316,16 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="16">
+      <c r="H9" s="15">
         <v>2</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <v>1</v>
       </c>
       <c r="J9" s="8">
         <v>1</v>
       </c>
-      <c r="K9" s="17" t="str">
+      <c r="K9" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;+.</v>
       </c>
@@ -1348,16 +1339,16 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-      <c r="S9" s="16">
+      <c r="S9" s="15">
         <v>-2</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T9" s="15">
         <v>1</v>
       </c>
       <c r="U9" s="8">
         <v>1</v>
       </c>
-      <c r="V9" s="17" t="str">
+      <c r="V9" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;&lt;+.</v>
       </c>
@@ -1371,16 +1362,16 @@
       <c r="AA9" s="5"/>
       <c r="AB9" s="5"/>
       <c r="AC9" s="5"/>
-      <c r="AD9" s="16">
+      <c r="AD9" s="15">
         <v>-1</v>
       </c>
-      <c r="AE9" s="16">
+      <c r="AE9" s="15">
         <v>1</v>
       </c>
       <c r="AF9" s="8">
         <v>1</v>
       </c>
-      <c r="AG9" s="17" t="str">
+      <c r="AG9" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;+.</v>
       </c>
@@ -1392,12 +1383,12 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
-      <c r="AO9" s="16"/>
-      <c r="AP9" s="16"/>
-      <c r="AQ9" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR9" s="17" t="str">
+      <c r="AO9" s="15"/>
+      <c r="AP9" s="15"/>
+      <c r="AQ9" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1416,16 +1407,16 @@
         <v>111</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <v>3</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="15">
         <v>1</v>
       </c>
       <c r="J10" s="8">
         <v>1</v>
       </c>
-      <c r="K10" s="17" t="str">
+      <c r="K10" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;&gt;+.</v>
       </c>
@@ -1439,16 +1430,16 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="16">
-        <v>1</v>
-      </c>
-      <c r="T10" s="16">
+      <c r="S10" s="15">
+        <v>1</v>
+      </c>
+      <c r="T10" s="15">
         <v>1</v>
       </c>
       <c r="U10" s="8">
         <v>1</v>
       </c>
-      <c r="V10" s="17" t="str">
+      <c r="V10" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;+.</v>
       </c>
@@ -1462,16 +1453,16 @@
       </c>
       <c r="AB10" s="5"/>
       <c r="AC10" s="5"/>
-      <c r="AD10" s="16">
+      <c r="AD10" s="15">
         <v>2</v>
       </c>
-      <c r="AE10" s="16">
+      <c r="AE10" s="15">
         <v>1</v>
       </c>
       <c r="AF10" s="8">
         <v>1</v>
       </c>
-      <c r="AG10" s="17" t="str">
+      <c r="AG10" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;&gt;+.</v>
       </c>
@@ -1483,12 +1474,12 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
-      <c r="AO10" s="16"/>
-      <c r="AP10" s="16"/>
-      <c r="AQ10" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR10" s="17" t="str">
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1507,16 +1498,16 @@
       <c r="G11" s="5">
         <v>108</v>
       </c>
-      <c r="H11" s="16">
-        <v>1</v>
-      </c>
-      <c r="I11" s="16">
+      <c r="H11" s="15">
+        <v>1</v>
+      </c>
+      <c r="I11" s="15">
         <v>0</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
       </c>
-      <c r="K11" s="17" t="str">
+      <c r="K11" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;.</v>
       </c>
@@ -1530,16 +1521,16 @@
         <v>108</v>
       </c>
       <c r="R11" s="5"/>
-      <c r="S11" s="16">
+      <c r="S11" s="15">
         <v>2</v>
       </c>
-      <c r="T11" s="16">
+      <c r="T11" s="15">
         <v>0</v>
       </c>
       <c r="U11" s="8">
         <v>1</v>
       </c>
-      <c r="V11" s="17" t="str">
+      <c r="V11" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;&gt;.</v>
       </c>
@@ -1553,16 +1544,16 @@
         <v>108</v>
       </c>
       <c r="AC11" s="5"/>
-      <c r="AD11" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="16">
+      <c r="AD11" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="15">
         <v>0</v>
       </c>
       <c r="AF11" s="8">
         <v>1</v>
       </c>
-      <c r="AG11" s="17" t="str">
+      <c r="AG11" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;.</v>
       </c>
@@ -1574,12 +1565,12 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="16"/>
-      <c r="AP11" s="16"/>
-      <c r="AQ11" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR11" s="17" t="str">
+      <c r="AO11" s="15"/>
+      <c r="AP11" s="15"/>
+      <c r="AQ11" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1598,16 +1589,16 @@
       <c r="G12" s="5">
         <v>109</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <v>0</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="15">
         <v>1</v>
       </c>
       <c r="J12" s="8">
         <v>1</v>
       </c>
-      <c r="K12" s="17" t="str">
+      <c r="K12" s="16" t="str">
         <f t="shared" si="0"/>
         <v>+.</v>
       </c>
@@ -1621,16 +1612,16 @@
         <v>109</v>
       </c>
       <c r="R12" s="5"/>
-      <c r="S12" s="16">
+      <c r="S12" s="15">
         <v>0</v>
       </c>
-      <c r="T12" s="16">
+      <c r="T12" s="15">
         <v>1</v>
       </c>
       <c r="U12" s="8">
         <v>1</v>
       </c>
-      <c r="V12" s="17" t="str">
+      <c r="V12" s="16" t="str">
         <f t="shared" si="1"/>
         <v>+.</v>
       </c>
@@ -1644,16 +1635,16 @@
         <v>109</v>
       </c>
       <c r="AC12" s="5"/>
-      <c r="AD12" s="16">
+      <c r="AD12" s="15">
         <v>0</v>
       </c>
-      <c r="AE12" s="16">
+      <c r="AE12" s="15">
         <v>1</v>
       </c>
       <c r="AF12" s="8">
         <v>1</v>
       </c>
-      <c r="AG12" s="17" t="str">
+      <c r="AG12" s="16" t="str">
         <f t="shared" si="2"/>
         <v>+.</v>
       </c>
@@ -1665,12 +1656,12 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="16"/>
-      <c r="AP12" s="16"/>
-      <c r="AQ12" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR12" s="17" t="str">
+      <c r="AO12" s="15"/>
+      <c r="AP12" s="15"/>
+      <c r="AQ12" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1689,16 +1680,16 @@
       <c r="G13" s="5">
         <v>105</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <v>0</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="15">
         <v>-4</v>
       </c>
       <c r="J13" s="8">
         <v>1</v>
       </c>
-      <c r="K13" s="17" t="str">
+      <c r="K13" s="16" t="str">
         <f t="shared" si="0"/>
         <v>----.</v>
       </c>
@@ -1712,16 +1703,16 @@
         <v>105</v>
       </c>
       <c r="R13" s="5"/>
-      <c r="S13" s="16">
+      <c r="S13" s="15">
         <v>0</v>
       </c>
-      <c r="T13" s="16">
+      <c r="T13" s="15">
         <v>-4</v>
       </c>
       <c r="U13" s="8">
         <v>1</v>
       </c>
-      <c r="V13" s="17" t="str">
+      <c r="V13" s="16" t="str">
         <f t="shared" si="1"/>
         <v>----.</v>
       </c>
@@ -1735,16 +1726,16 @@
         <v>105</v>
       </c>
       <c r="AC13" s="5"/>
-      <c r="AD13" s="16">
+      <c r="AD13" s="15">
         <v>0</v>
       </c>
-      <c r="AE13" s="16">
+      <c r="AE13" s="15">
         <v>-4</v>
       </c>
       <c r="AF13" s="8">
         <v>1</v>
       </c>
-      <c r="AG13" s="17" t="str">
+      <c r="AG13" s="16" t="str">
         <f t="shared" si="2"/>
         <v>----.</v>
       </c>
@@ -1756,12 +1747,12 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="16"/>
-      <c r="AP13" s="16"/>
-      <c r="AQ13" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR13" s="17" t="str">
+      <c r="AO13" s="15"/>
+      <c r="AP13" s="15"/>
+      <c r="AQ13" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1780,16 +1771,16 @@
         <v>115</v>
       </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="16">
-        <v>1</v>
-      </c>
-      <c r="I14" s="16">
+      <c r="H14" s="15">
+        <v>1</v>
+      </c>
+      <c r="I14" s="15">
         <v>4</v>
       </c>
       <c r="J14" s="8">
         <v>1</v>
       </c>
-      <c r="K14" s="17" t="str">
+      <c r="K14" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;++++.</v>
       </c>
@@ -1803,16 +1794,16 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="16">
+      <c r="S14" s="15">
         <v>-2</v>
       </c>
-      <c r="T14" s="16">
+      <c r="T14" s="15">
         <v>4</v>
       </c>
       <c r="U14" s="8">
         <v>1</v>
       </c>
-      <c r="V14" s="17" t="str">
+      <c r="V14" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;&lt;++++.</v>
       </c>
@@ -1826,16 +1817,16 @@
       </c>
       <c r="AB14" s="5"/>
       <c r="AC14" s="5"/>
-      <c r="AD14" s="16">
+      <c r="AD14" s="15">
         <v>-1</v>
       </c>
-      <c r="AE14" s="16">
+      <c r="AE14" s="15">
         <v>4</v>
       </c>
       <c r="AF14" s="8">
         <v>1</v>
       </c>
-      <c r="AG14" s="17" t="str">
+      <c r="AG14" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;++++.</v>
       </c>
@@ -1847,12 +1838,12 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="16"/>
-      <c r="AP14" s="16"/>
-      <c r="AQ14" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR14" s="17" t="str">
+      <c r="AO14" s="15"/>
+      <c r="AP14" s="15"/>
+      <c r="AQ14" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR14" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1871,16 +1862,16 @@
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="16">
-        <v>1</v>
-      </c>
-      <c r="I15" s="16">
+      <c r="H15" s="15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="15">
         <v>-4</v>
       </c>
       <c r="J15" s="8">
         <v>1</v>
       </c>
-      <c r="K15" s="17" t="str">
+      <c r="K15" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;----.</v>
       </c>
@@ -1894,16 +1885,16 @@
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
-      <c r="S15" s="16">
-        <v>1</v>
-      </c>
-      <c r="T15" s="16">
+      <c r="S15" s="15">
+        <v>1</v>
+      </c>
+      <c r="T15" s="15">
         <v>-4</v>
       </c>
       <c r="U15" s="8">
         <v>1</v>
       </c>
-      <c r="V15" s="17" t="str">
+      <c r="V15" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;----.</v>
       </c>
@@ -1917,16 +1908,16 @@
       <c r="AA15" s="5"/>
       <c r="AB15" s="5"/>
       <c r="AC15" s="5"/>
-      <c r="AD15" s="16">
+      <c r="AD15" s="15">
         <v>-1</v>
       </c>
-      <c r="AE15" s="16">
+      <c r="AE15" s="15">
         <v>-4</v>
       </c>
       <c r="AF15" s="8">
         <v>1</v>
       </c>
-      <c r="AG15" s="17" t="str">
+      <c r="AG15" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;----.</v>
       </c>
@@ -1938,12 +1929,12 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="16"/>
-      <c r="AP15" s="16"/>
-      <c r="AQ15" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR15" s="17" t="str">
+      <c r="AO15" s="15"/>
+      <c r="AP15" s="15"/>
+      <c r="AQ15" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR15" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -1962,16 +1953,16 @@
         <v>110</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="16">
+      <c r="H16" s="15">
+        <v>1</v>
+      </c>
+      <c r="I16" s="15">
         <v>-5</v>
       </c>
       <c r="J16" s="8">
         <v>1</v>
       </c>
-      <c r="K16" s="17" t="str">
+      <c r="K16" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;-----.</v>
       </c>
@@ -1985,16 +1976,16 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
-      <c r="S16" s="16">
+      <c r="S16" s="15">
         <v>-1</v>
       </c>
-      <c r="T16" s="16">
+      <c r="T16" s="15">
         <v>-5</v>
       </c>
       <c r="U16" s="8">
         <v>1</v>
       </c>
-      <c r="V16" s="17" t="str">
+      <c r="V16" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;-----.</v>
       </c>
@@ -2008,16 +1999,16 @@
       </c>
       <c r="AB16" s="5"/>
       <c r="AC16" s="5"/>
-      <c r="AD16" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE16" s="16">
+      <c r="AD16" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="15">
         <v>-5</v>
       </c>
       <c r="AF16" s="8">
         <v>1</v>
       </c>
-      <c r="AG16" s="17" t="str">
+      <c r="AG16" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;-----.</v>
       </c>
@@ -2029,12 +2020,12 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="16"/>
-      <c r="AP16" s="16"/>
-      <c r="AQ16" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR16" s="17" t="str">
+      <c r="AO16" s="15"/>
+      <c r="AP16" s="15"/>
+      <c r="AQ16" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR16" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2053,16 +2044,16 @@
       <c r="G17" s="5">
         <v>105</v>
       </c>
-      <c r="H17" s="16">
-        <v>1</v>
-      </c>
-      <c r="I17" s="16">
+      <c r="H17" s="15">
+        <v>1</v>
+      </c>
+      <c r="I17" s="15">
         <v>0</v>
       </c>
       <c r="J17" s="8">
         <v>1</v>
       </c>
-      <c r="K17" s="17" t="str">
+      <c r="K17" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;.</v>
       </c>
@@ -2076,16 +2067,16 @@
         <v>105</v>
       </c>
       <c r="R17" s="5"/>
-      <c r="S17" s="16">
+      <c r="S17" s="15">
         <v>2</v>
       </c>
-      <c r="T17" s="16">
+      <c r="T17" s="15">
         <v>0</v>
       </c>
       <c r="U17" s="8">
         <v>1</v>
       </c>
-      <c r="V17" s="17" t="str">
+      <c r="V17" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;&gt;.</v>
       </c>
@@ -2099,16 +2090,16 @@
         <v>105</v>
       </c>
       <c r="AC17" s="5"/>
-      <c r="AD17" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="16">
+      <c r="AD17" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="15">
         <v>0</v>
       </c>
       <c r="AF17" s="8">
         <v>1</v>
       </c>
-      <c r="AG17" s="17" t="str">
+      <c r="AG17" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;.</v>
       </c>
@@ -2120,12 +2111,12 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="16"/>
-      <c r="AP17" s="16"/>
-      <c r="AQ17" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR17" s="17" t="str">
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR17" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2144,16 +2135,16 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <v>3</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="15">
         <v>1</v>
       </c>
       <c r="J18" s="8">
         <v>1</v>
       </c>
-      <c r="K18" s="17" t="str">
+      <c r="K18" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;&gt;+.</v>
       </c>
@@ -2167,16 +2158,16 @@
       <c r="R18" s="5">
         <v>64</v>
       </c>
-      <c r="S18" s="16">
-        <v>1</v>
-      </c>
-      <c r="T18" s="16">
+      <c r="S18" s="15">
+        <v>1</v>
+      </c>
+      <c r="T18" s="15">
         <v>1</v>
       </c>
       <c r="U18" s="8">
         <v>1</v>
       </c>
-      <c r="V18" s="17" t="str">
+      <c r="V18" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;+.</v>
       </c>
@@ -2190,16 +2181,16 @@
       <c r="AC18" s="5">
         <v>64</v>
       </c>
-      <c r="AD18" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE18" s="16">
+      <c r="AD18" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="15">
         <v>1</v>
       </c>
       <c r="AF18" s="8">
         <v>1</v>
       </c>
-      <c r="AG18" s="17" t="str">
+      <c r="AG18" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;+.</v>
       </c>
@@ -2211,12 +2202,12 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="16"/>
-      <c r="AP18" s="16"/>
-      <c r="AQ18" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR18" s="17" t="str">
+      <c r="AO18" s="15"/>
+      <c r="AP18" s="15"/>
+      <c r="AQ18" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR18" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2235,16 +2226,16 @@
       <c r="G19" s="5">
         <v>103</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="15">
         <v>3</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="15">
         <v>-2</v>
       </c>
       <c r="J19" s="8">
         <v>1</v>
       </c>
-      <c r="K19" s="17" t="str">
+      <c r="K19" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;&gt;--.</v>
       </c>
@@ -2258,16 +2249,16 @@
         <v>103</v>
       </c>
       <c r="R19" s="5"/>
-      <c r="S19" s="16">
+      <c r="S19" s="15">
         <v>-1</v>
       </c>
-      <c r="T19" s="16">
+      <c r="T19" s="15">
         <v>-2</v>
       </c>
       <c r="U19" s="8">
         <v>1</v>
       </c>
-      <c r="V19" s="17" t="str">
+      <c r="V19" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;--.</v>
       </c>
@@ -2281,16 +2272,16 @@
         <v>103</v>
       </c>
       <c r="AC19" s="5"/>
-      <c r="AD19" s="16">
+      <c r="AD19" s="15">
         <v>-1</v>
       </c>
-      <c r="AE19" s="16">
+      <c r="AE19" s="15">
         <v>-2</v>
       </c>
       <c r="AF19" s="8">
         <v>1</v>
       </c>
-      <c r="AG19" s="17" t="str">
+      <c r="AG19" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;--.</v>
       </c>
@@ -2302,12 +2293,12 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
-      <c r="AO19" s="16"/>
-      <c r="AP19" s="16"/>
-      <c r="AQ19" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR19" s="17" t="str">
+      <c r="AO19" s="15"/>
+      <c r="AP19" s="15"/>
+      <c r="AQ19" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR19" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2326,16 +2317,16 @@
         <v>109</v>
       </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="16">
-        <v>1</v>
-      </c>
-      <c r="I20" s="16">
+      <c r="H20" s="15">
+        <v>1</v>
+      </c>
+      <c r="I20" s="15">
         <v>-1</v>
       </c>
       <c r="J20" s="8">
         <v>1</v>
       </c>
-      <c r="K20" s="17" t="str">
+      <c r="K20" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;-.</v>
       </c>
@@ -2349,16 +2340,16 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
-      <c r="S20" s="16">
+      <c r="S20" s="15">
         <v>-2</v>
       </c>
-      <c r="T20" s="16">
+      <c r="T20" s="15">
         <v>-1</v>
       </c>
       <c r="U20" s="8">
         <v>1</v>
       </c>
-      <c r="V20" s="17" t="str">
+      <c r="V20" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;&lt;-.</v>
       </c>
@@ -2372,16 +2363,16 @@
       </c>
       <c r="AB20" s="5"/>
       <c r="AC20" s="5"/>
-      <c r="AD20" s="16">
+      <c r="AD20" s="15">
         <v>-1</v>
       </c>
-      <c r="AE20" s="16">
+      <c r="AE20" s="15">
         <v>-1</v>
       </c>
       <c r="AF20" s="8">
         <v>1</v>
       </c>
-      <c r="AG20" s="17" t="str">
+      <c r="AG20" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;-.</v>
       </c>
@@ -2393,12 +2384,12 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="16"/>
-      <c r="AP20" s="16"/>
-      <c r="AQ20" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR20" s="17" t="str">
+      <c r="AO20" s="15"/>
+      <c r="AP20" s="15"/>
+      <c r="AQ20" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2417,16 +2408,16 @@
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="16">
-        <v>1</v>
-      </c>
-      <c r="I21" s="16">
+      <c r="H21" s="15">
+        <v>1</v>
+      </c>
+      <c r="I21" s="15">
         <v>0</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
       </c>
-      <c r="K21" s="17" t="str">
+      <c r="K21" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;.</v>
       </c>
@@ -2440,16 +2431,16 @@
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
-      <c r="S21" s="16">
-        <v>1</v>
-      </c>
-      <c r="T21" s="16">
+      <c r="S21" s="15">
+        <v>1</v>
+      </c>
+      <c r="T21" s="15">
         <v>0</v>
       </c>
       <c r="U21" s="8">
         <v>1</v>
       </c>
-      <c r="V21" s="17" t="str">
+      <c r="V21" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;.</v>
       </c>
@@ -2463,16 +2454,16 @@
       <c r="AA21" s="5"/>
       <c r="AB21" s="5"/>
       <c r="AC21" s="5"/>
-      <c r="AD21" s="16">
+      <c r="AD21" s="15">
         <v>-1</v>
       </c>
-      <c r="AE21" s="16">
+      <c r="AE21" s="15">
         <v>0</v>
       </c>
       <c r="AF21" s="8">
         <v>1</v>
       </c>
-      <c r="AG21" s="17" t="str">
+      <c r="AG21" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;.</v>
       </c>
@@ -2484,12 +2475,12 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="16"/>
-      <c r="AP21" s="16"/>
-      <c r="AQ21" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR21" s="17" t="str">
+      <c r="AO21" s="15"/>
+      <c r="AP21" s="15"/>
+      <c r="AQ21" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR21" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2508,16 +2499,16 @@
       <c r="G22" s="5">
         <v>105</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="15">
         <v>2</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="15">
         <v>2</v>
       </c>
       <c r="J22" s="8">
         <v>1</v>
       </c>
-      <c r="K22" s="17" t="str">
+      <c r="K22" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;++.</v>
       </c>
@@ -2531,16 +2522,16 @@
         <v>105</v>
       </c>
       <c r="R22" s="5"/>
-      <c r="S22" s="16">
-        <v>1</v>
-      </c>
-      <c r="T22" s="16">
+      <c r="S22" s="15">
+        <v>1</v>
+      </c>
+      <c r="T22" s="15">
         <v>2</v>
       </c>
       <c r="U22" s="8">
         <v>1</v>
       </c>
-      <c r="V22" s="17" t="str">
+      <c r="V22" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;++.</v>
       </c>
@@ -2554,16 +2545,16 @@
         <v>105</v>
       </c>
       <c r="AC22" s="5"/>
-      <c r="AD22" s="16">
+      <c r="AD22" s="15">
         <v>2</v>
       </c>
-      <c r="AE22" s="16">
+      <c r="AE22" s="15">
         <v>2</v>
       </c>
       <c r="AF22" s="8">
         <v>1</v>
       </c>
-      <c r="AG22" s="17" t="str">
+      <c r="AG22" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;&gt;++.</v>
       </c>
@@ -2575,12 +2566,12 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="16"/>
-      <c r="AP22" s="16"/>
-      <c r="AQ22" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR22" s="17" t="str">
+      <c r="AO22" s="15"/>
+      <c r="AP22" s="15"/>
+      <c r="AQ22" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR22" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2599,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="G23" s="5"/>
-      <c r="H23" s="16">
-        <v>1</v>
-      </c>
-      <c r="I23" s="16">
+      <c r="H23" s="15">
+        <v>1</v>
+      </c>
+      <c r="I23" s="15">
         <v>-1</v>
       </c>
       <c r="J23" s="8">
         <v>1</v>
       </c>
-      <c r="K23" s="17" t="str">
+      <c r="K23" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;-.</v>
       </c>
@@ -2622,16 +2613,16 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
-      <c r="S23" s="16">
+      <c r="S23" s="15">
         <v>-2</v>
       </c>
-      <c r="T23" s="16">
+      <c r="T23" s="15">
         <v>-1</v>
       </c>
       <c r="U23" s="8">
         <v>1</v>
       </c>
-      <c r="V23" s="17" t="str">
+      <c r="V23" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;&lt;-.</v>
       </c>
@@ -2645,16 +2636,16 @@
       </c>
       <c r="AB23" s="5"/>
       <c r="AC23" s="5"/>
-      <c r="AD23" s="16">
+      <c r="AD23" s="15">
         <v>-1</v>
       </c>
-      <c r="AE23" s="16">
+      <c r="AE23" s="15">
         <v>-1</v>
       </c>
       <c r="AF23" s="8">
         <v>1</v>
       </c>
-      <c r="AG23" s="17" t="str">
+      <c r="AG23" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;-.</v>
       </c>
@@ -2666,12 +2657,12 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="16"/>
-      <c r="AP23" s="16"/>
-      <c r="AQ23" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR23" s="17" t="str">
+      <c r="AO23" s="15"/>
+      <c r="AP23" s="15"/>
+      <c r="AQ23" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR23" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2690,16 +2681,16 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="16">
+      <c r="H24" s="15">
         <v>3</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="15">
         <v>0</v>
       </c>
       <c r="J24" s="8">
         <v>1</v>
       </c>
-      <c r="K24" s="17" t="str">
+      <c r="K24" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;&gt;.</v>
       </c>
@@ -2713,16 +2704,16 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
-      <c r="S24" s="16">
+      <c r="S24" s="15">
         <v>-1</v>
       </c>
-      <c r="T24" s="16">
+      <c r="T24" s="15">
         <v>0</v>
       </c>
       <c r="U24" s="8">
         <v>1</v>
       </c>
-      <c r="V24" s="17" t="str">
+      <c r="V24" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;.</v>
       </c>
@@ -2736,16 +2727,16 @@
       <c r="AA24" s="5"/>
       <c r="AB24" s="5"/>
       <c r="AC24" s="5"/>
-      <c r="AD24" s="16">
+      <c r="AD24" s="15">
         <v>-2</v>
       </c>
-      <c r="AE24" s="16">
+      <c r="AE24" s="15">
         <v>0</v>
       </c>
       <c r="AF24" s="8">
         <v>1</v>
       </c>
-      <c r="AG24" s="17" t="str">
+      <c r="AG24" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&lt;&lt;.</v>
       </c>
@@ -2757,12 +2748,12 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="16"/>
-      <c r="AP24" s="16"/>
-      <c r="AQ24" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR24" s="17" t="str">
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR24" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2781,16 +2772,16 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="16">
+      <c r="H25" s="15">
         <v>2</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="15">
         <v>2</v>
       </c>
       <c r="J25" s="8">
         <v>1</v>
       </c>
-      <c r="K25" s="17" t="str">
+      <c r="K25" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;&gt;++.</v>
       </c>
@@ -2804,16 +2795,16 @@
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
-      <c r="S25" s="16">
+      <c r="S25" s="15">
         <v>2</v>
       </c>
-      <c r="T25" s="16">
+      <c r="T25" s="15">
         <v>2</v>
       </c>
       <c r="U25" s="8">
         <v>1</v>
       </c>
-      <c r="V25" s="17" t="str">
+      <c r="V25" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&gt;&gt;++.</v>
       </c>
@@ -2827,16 +2818,16 @@
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
       <c r="AC25" s="5"/>
-      <c r="AD25" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE25" s="16">
+      <c r="AD25" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="15">
         <v>2</v>
       </c>
       <c r="AF25" s="8">
         <v>1</v>
       </c>
-      <c r="AG25" s="17" t="str">
+      <c r="AG25" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;++.</v>
       </c>
@@ -2848,12 +2839,12 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
-      <c r="AO25" s="16"/>
-      <c r="AP25" s="16"/>
-      <c r="AQ25" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR25" s="17" t="str">
+      <c r="AO25" s="15"/>
+      <c r="AP25" s="15"/>
+      <c r="AQ25" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR25" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2872,16 +2863,16 @@
         <v>111</v>
       </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="16">
-        <v>1</v>
-      </c>
-      <c r="I26" s="16">
+      <c r="H26" s="15">
+        <v>1</v>
+      </c>
+      <c r="I26" s="15">
         <v>3</v>
       </c>
       <c r="J26" s="8">
         <v>1</v>
       </c>
-      <c r="K26" s="17" t="str">
+      <c r="K26" s="16" t="str">
         <f t="shared" si="0"/>
         <v>&gt;+++.</v>
       </c>
@@ -2895,16 +2886,16 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-      <c r="S26" s="16">
+      <c r="S26" s="15">
         <v>-1</v>
       </c>
-      <c r="T26" s="16">
+      <c r="T26" s="15">
         <v>3</v>
       </c>
       <c r="U26" s="8">
         <v>1</v>
       </c>
-      <c r="V26" s="17" t="str">
+      <c r="V26" s="16" t="str">
         <f t="shared" si="1"/>
         <v>&lt;+++.</v>
       </c>
@@ -2918,16 +2909,16 @@
       </c>
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
-      <c r="AD26" s="16">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="16">
+      <c r="AD26" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="15">
         <v>3</v>
       </c>
       <c r="AF26" s="8">
         <v>1</v>
       </c>
-      <c r="AG26" s="17" t="str">
+      <c r="AG26" s="16" t="str">
         <f t="shared" si="2"/>
         <v>&gt;+++.</v>
       </c>
@@ -2939,12 +2930,12 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
-      <c r="AO26" s="16"/>
-      <c r="AP26" s="16"/>
-      <c r="AQ26" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR26" s="17" t="str">
+      <c r="AO26" s="15"/>
+      <c r="AP26" s="15"/>
+      <c r="AQ26" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR26" s="16" t="str">
         <f t="shared" si="3"/>
         <v>.</v>
       </c>
@@ -2963,16 +2954,16 @@
         <v>109</v>
       </c>
       <c r="G27" s="5"/>
-      <c r="H27" s="16">
+      <c r="H27" s="15">
         <v>0</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="15">
         <v>-2</v>
       </c>
       <c r="J27" s="8">
         <v>1</v>
       </c>
-      <c r="K27" s="17" t="str">
+      <c r="K27" s="16" t="str">
         <f>_xlfn.CONCAT(REPT(IF(H27&gt;0,"&gt;","&lt;"),ABS(H27)),REPT(IF(I27&gt;0,"+","-"),ABS(I27)),".")</f>
         <v>--.</v>
       </c>
@@ -2986,16 +2977,16 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
-      <c r="S27" s="16">
+      <c r="S27" s="15">
         <v>0</v>
       </c>
-      <c r="T27" s="16">
+      <c r="T27" s="15">
         <v>-2</v>
       </c>
       <c r="U27" s="8">
         <v>1</v>
       </c>
-      <c r="V27" s="17" t="str">
+      <c r="V27" s="16" t="str">
         <f>_xlfn.CONCAT(REPT(IF(S27&gt;0,"&gt;","&lt;"),ABS(S27)),REPT(IF(T27&gt;0,"+","-"),ABS(T27)),".")</f>
         <v>--.</v>
       </c>
@@ -3009,16 +3000,16 @@
       </c>
       <c r="AB27" s="5"/>
       <c r="AC27" s="5"/>
-      <c r="AD27" s="16">
+      <c r="AD27" s="15">
         <v>0</v>
       </c>
-      <c r="AE27" s="16">
+      <c r="AE27" s="15">
         <v>-2</v>
       </c>
       <c r="AF27" s="8">
         <v>1</v>
       </c>
-      <c r="AG27" s="17" t="str">
+      <c r="AG27" s="16" t="str">
         <f>_xlfn.CONCAT(REPT(IF(AD27&gt;0,"&gt;","&lt;"),ABS(AD27)),REPT(IF(AE27&gt;0,"+","-"),ABS(AE27)),".")</f>
         <v>--.</v>
       </c>
@@ -3030,12 +3021,12 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
-      <c r="AO27" s="16"/>
-      <c r="AP27" s="16"/>
-      <c r="AQ27" s="15">
-        <v>1</v>
-      </c>
-      <c r="AR27" s="17" t="str">
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="8">
+        <v>1</v>
+      </c>
+      <c r="AR27" s="16" t="str">
         <f>_xlfn.CONCAT(REPT(IF(AO27&gt;0,"&gt;","&lt;"),ABS(AO27)),REPT(IF(AP27&gt;0,"+","-"),ABS(AP27)),".")</f>
         <v>.</v>
       </c>
@@ -3081,8 +3072,8 @@
         <v>26</v>
       </c>
       <c r="V28" s="11">
-        <f>S28+T28+U28+69</f>
-        <v>177</v>
+        <f>S28+T28+U28+46</f>
+        <v>154</v>
       </c>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
@@ -3102,8 +3093,8 @@
         <v>26</v>
       </c>
       <c r="AG28" s="11">
-        <f>AD28+AE28+AF28+69</f>
-        <v>174</v>
+        <f>AD28+AE28+AF28+46</f>
+        <v>151</v>
       </c>
       <c r="AJ28" s="5"/>
       <c r="AK28" s="5"/>
@@ -3123,8 +3114,8 @@
         <v>26</v>
       </c>
       <c r="AR28" s="11">
-        <f>AO28+AP28+AQ28+69</f>
-        <v>95</v>
+        <f>AO28+AP28+AQ28+46</f>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
